--- a/stacked_model/results/validation/monte_carlo_error_propagation/mc_error_propagation_fold_results.xlsx
+++ b/stacked_model/results/validation/monte_carlo_error_propagation/mc_error_propagation_fold_results.xlsx
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -588,28 +588,28 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O2" t="n">
         <v>2000</v>
       </c>
       <c r="P2" t="n">
-        <v>2.209122294606164</v>
+        <v>2.699151939426058</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.247419264759777</v>
+        <v>2.394829680744282</v>
       </c>
       <c r="R2" t="n">
-        <v>1.047847391452004</v>
+        <v>0.828986437928581</v>
       </c>
       <c r="S2" t="n">
-        <v>1.265548773021532</v>
+        <v>1.026913595253121</v>
       </c>
       <c r="T2" t="n">
-        <v>2.827172395376095</v>
+        <v>2.293075832951146</v>
       </c>
       <c r="U2" t="n">
-        <v>3.967132368394298</v>
+        <v>4.022934203221011</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -665,28 +665,28 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O3" t="n">
         <v>2000</v>
       </c>
       <c r="P3" t="n">
-        <v>2.703398616230706</v>
+        <v>2.564100117591577</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.49409952323724</v>
+        <v>2.611463231684498</v>
       </c>
       <c r="R3" t="n">
-        <v>1.022223661964284</v>
+        <v>0.9867184438971841</v>
       </c>
       <c r="S3" t="n">
-        <v>1.45815895672521</v>
+        <v>1.441903299202847</v>
       </c>
       <c r="T3" t="n">
-        <v>4.138319907208711</v>
+        <v>3.886210946791742</v>
       </c>
       <c r="U3" t="n">
-        <v>3.922986231019305</v>
+        <v>4.128081463156676</v>
       </c>
     </row>
     <row r="4">
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -742,28 +742,28 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O4" t="n">
         <v>2000</v>
       </c>
       <c r="P4" t="n">
-        <v>2.411867210737011</v>
+        <v>2.58153479272315</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.160547067727915</v>
+        <v>2.018885973540915</v>
       </c>
       <c r="R4" t="n">
-        <v>0.89455163540492</v>
+        <v>1.13003805137548</v>
       </c>
       <c r="S4" t="n">
-        <v>1.185841772318655</v>
+        <v>1.40162869807929</v>
       </c>
       <c r="T4" t="n">
-        <v>3.903035714918275</v>
+        <v>3.357478379424592</v>
       </c>
       <c r="U4" t="n">
-        <v>4.127234768297448</v>
+        <v>3.84240950027858</v>
       </c>
     </row>
     <row r="5">
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -819,28 +819,28 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O5" t="n">
         <v>2000</v>
       </c>
       <c r="P5" t="n">
-        <v>2.658066534212547</v>
+        <v>2.867677214304657</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.447287723542784</v>
+        <v>2.539039525317597</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7924017122081026</v>
+        <v>1.009538434352825</v>
       </c>
       <c r="S5" t="n">
-        <v>1.000482007688696</v>
+        <v>1.33590398003001</v>
       </c>
       <c r="T5" t="n">
-        <v>2.357478195125815</v>
+        <v>3.988128387393438</v>
       </c>
       <c r="U5" t="n">
-        <v>3.828211400279056</v>
+        <v>3.955102784311684</v>
       </c>
     </row>
     <row r="6">
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -896,28 +896,28 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O6" t="n">
         <v>2000</v>
       </c>
       <c r="P6" t="n">
-        <v>2.471223982856794</v>
+        <v>2.4638401998892</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.276299350099816</v>
+        <v>1.852922805344331</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6657273764539348</v>
+        <v>0.7776639082687348</v>
       </c>
       <c r="S6" t="n">
-        <v>1.027092038342434</v>
+        <v>1.080931550963814</v>
       </c>
       <c r="T6" t="n">
-        <v>3.01981778488296</v>
+        <v>3.025407572383159</v>
       </c>
       <c r="U6" t="n">
-        <v>3.794306261263467</v>
+        <v>3.891726423382819</v>
       </c>
     </row>
     <row r="7">
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -973,28 +973,28 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O7" t="n">
         <v>2000</v>
       </c>
       <c r="P7" t="n">
-        <v>2.000001077085538</v>
+        <v>2.388532641165372</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.859915643368241</v>
+        <v>2.122708193489948</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4768759319629758</v>
+        <v>0.4712148495519942</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6368257133854625</v>
+        <v>0.5835294975516659</v>
       </c>
       <c r="T7" t="n">
-        <v>2.030578252915156</v>
+        <v>1.313796665318641</v>
       </c>
       <c r="U7" t="n">
-        <v>3.543261730698576</v>
+        <v>3.601784768865184</v>
       </c>
     </row>
     <row r="8">
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1050,28 +1050,28 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O8" t="n">
         <v>2000</v>
       </c>
       <c r="P8" t="n">
-        <v>3.468267180254506</v>
+        <v>2.272070409742034</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.891220158109658</v>
+        <v>2.249684044264631</v>
       </c>
       <c r="R8" t="n">
-        <v>1.601273670059165</v>
+        <v>0.825178418496001</v>
       </c>
       <c r="S8" t="n">
-        <v>2.206855107112629</v>
+        <v>1.025561237787433</v>
       </c>
       <c r="T8" t="n">
-        <v>5.278114516936569</v>
+        <v>2.099337205926766</v>
       </c>
       <c r="U8" t="n">
-        <v>3.994410222093524</v>
+        <v>3.843519561515597</v>
       </c>
     </row>
     <row r="9">
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1127,28 +1127,28 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O9" t="n">
         <v>2000</v>
       </c>
       <c r="P9" t="n">
-        <v>2.927934198385839</v>
+        <v>2.860944247652724</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.835390870588101</v>
+        <v>2.613327592891876</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8107530719403493</v>
+        <v>0.8679524655165306</v>
       </c>
       <c r="S9" t="n">
-        <v>1.081022498425912</v>
+        <v>1.178811297161007</v>
       </c>
       <c r="T9" t="n">
-        <v>2.992919313871901</v>
+        <v>3.22779199946708</v>
       </c>
       <c r="U9" t="n">
-        <v>3.787065347440967</v>
+        <v>3.934374739507598</v>
       </c>
     </row>
     <row r="10">
@@ -1172,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1204,28 +1204,28 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O10" t="n">
         <v>2000</v>
       </c>
       <c r="P10" t="n">
-        <v>2.998733648609572</v>
+        <v>2.43886418409505</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.390661523870364</v>
+        <v>2.102742645252307</v>
       </c>
       <c r="R10" t="n">
-        <v>1.405713513747305</v>
+        <v>1.119840149966239</v>
       </c>
       <c r="S10" t="n">
-        <v>1.661273971738894</v>
+        <v>1.341206509714205</v>
       </c>
       <c r="T10" t="n">
-        <v>3.16772160541155</v>
+        <v>2.66213618463987</v>
       </c>
       <c r="U10" t="n">
-        <v>4.313072853501137</v>
+        <v>4.319994723513085</v>
       </c>
     </row>
     <row r="11">
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O11" t="n">
         <v>2000</v>
       </c>
       <c r="P11" t="n">
-        <v>2.716308325716124</v>
+        <v>2.586416595330583</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.412407229145745</v>
+        <v>2.406095916459499</v>
       </c>
       <c r="R11" t="n">
-        <v>1.034941894593987</v>
+        <v>0.9578841891730218</v>
       </c>
       <c r="S11" t="n">
-        <v>1.411044670977258</v>
+        <v>1.348115364821993</v>
       </c>
       <c r="T11" t="n">
-        <v>4.198575187364405</v>
+        <v>4.357591439848584</v>
       </c>
       <c r="U11" t="n">
-        <v>4.049270585692242</v>
+        <v>3.972422737859654</v>
       </c>
     </row>
     <row r="12">
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1358,28 +1358,28 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O12" t="n">
         <v>2000</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08275282217471</v>
+        <v>2.06127089712946</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.438581735279386</v>
+        <v>1.345347046731189</v>
       </c>
       <c r="R12" t="n">
-        <v>0.925188633592725</v>
+        <v>0.8617841370018562</v>
       </c>
       <c r="S12" t="n">
-        <v>1.367973472120072</v>
+        <v>1.346501815760213</v>
       </c>
       <c r="T12" t="n">
-        <v>3.749884622641147</v>
+        <v>3.609519219402486</v>
       </c>
       <c r="U12" t="n">
-        <v>3.601648666951885</v>
+        <v>3.445012574752543</v>
       </c>
     </row>
     <row r="13">
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1435,28 +1435,28 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O13" t="n">
         <v>2000</v>
       </c>
       <c r="P13" t="n">
-        <v>2.379918731289764</v>
+        <v>2.287312454729531</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.134169775336309</v>
+        <v>2.195701237470053</v>
       </c>
       <c r="R13" t="n">
-        <v>0.842156798361627</v>
+        <v>0.7286862658414094</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1352456796815</v>
+        <v>0.8993752442336657</v>
       </c>
       <c r="T13" t="n">
-        <v>3.144991322339045</v>
+        <v>2.290939023388461</v>
       </c>
       <c r="U13" t="n">
-        <v>4.167365369820324</v>
+        <v>3.789574707225954</v>
       </c>
     </row>
     <row r="14">
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1512,28 +1512,28 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O14" t="n">
         <v>2000</v>
       </c>
       <c r="P14" t="n">
-        <v>2.672533833873386</v>
+        <v>2.52846826808816</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.808578790028453</v>
+        <v>2.689526003312011</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7257089833725727</v>
+        <v>0.8032810042161609</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8866916842851897</v>
+        <v>1.009106772416156</v>
       </c>
       <c r="T14" t="n">
-        <v>2.040154183481015</v>
+        <v>2.361992651410631</v>
       </c>
       <c r="U14" t="n">
-        <v>3.887788195048512</v>
+        <v>4.031769364183833</v>
       </c>
     </row>
     <row r="15">
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1589,28 +1589,28 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O15" t="n">
         <v>2000</v>
       </c>
       <c r="P15" t="n">
-        <v>2.870361803200385</v>
+        <v>2.803159410700434</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.781937063459224</v>
+        <v>2.786081198717349</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18202269348755</v>
+        <v>1.222351015925821</v>
       </c>
       <c r="S15" t="n">
-        <v>1.528703219782793</v>
+        <v>1.553860788687266</v>
       </c>
       <c r="T15" t="n">
-        <v>3.47903746354762</v>
+        <v>3.300743007251498</v>
       </c>
       <c r="U15" t="n">
-        <v>4.509006935240946</v>
+        <v>4.562702367204523</v>
       </c>
     </row>
     <row r="16">
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1666,28 +1666,28 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O16" t="n">
         <v>2000</v>
       </c>
       <c r="P16" t="n">
-        <v>2.633741670480625</v>
+        <v>2.596582768094624</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.463461876608242</v>
+        <v>2.143314687112775</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6412063622211013</v>
+        <v>0.716515581338235</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8306909523798355</v>
+        <v>0.9074106480189817</v>
       </c>
       <c r="T16" t="n">
-        <v>2.404987950442091</v>
+        <v>2.865836544580311</v>
       </c>
       <c r="U16" t="n">
-        <v>3.822758367943563</v>
+        <v>3.809048727523499</v>
       </c>
     </row>
     <row r="17">
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1743,28 +1743,28 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O17" t="n">
         <v>2000</v>
       </c>
       <c r="P17" t="n">
-        <v>2.302929089135886</v>
+        <v>2.238004368354498</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.218354986969302</v>
+        <v>1.80592327190976</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6873382819217767</v>
+        <v>0.6212921044027283</v>
       </c>
       <c r="S17" t="n">
-        <v>0.991819639327964</v>
+        <v>0.9010233654186811</v>
       </c>
       <c r="T17" t="n">
-        <v>2.318454867533305</v>
+        <v>2.482727854395371</v>
       </c>
       <c r="U17" t="n">
-        <v>4.351494925483022</v>
+        <v>3.888746305556668</v>
       </c>
     </row>
     <row r="18">
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1820,28 +1820,28 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O18" t="n">
         <v>2000</v>
       </c>
       <c r="P18" t="n">
-        <v>3.503574825677988</v>
+        <v>3.489765039824828</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.244994206793927</v>
+        <v>3.390696374890485</v>
       </c>
       <c r="R18" t="n">
-        <v>1.432724777636448</v>
+        <v>1.473368463500559</v>
       </c>
       <c r="S18" t="n">
-        <v>1.841824627450845</v>
+        <v>1.938441066743564</v>
       </c>
       <c r="T18" t="n">
-        <v>4.467649593649014</v>
+        <v>5.127092569142967</v>
       </c>
       <c r="U18" t="n">
-        <v>4.068829787540903</v>
+        <v>4.41531842634704</v>
       </c>
     </row>
     <row r="19">
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1897,28 +1897,28 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O19" t="n">
         <v>2000</v>
       </c>
       <c r="P19" t="n">
-        <v>2.435676238055333</v>
+        <v>2.58281705631045</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.318241473905095</v>
+        <v>2.73864239538318</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9226843084031539</v>
+        <v>0.8886858980168973</v>
       </c>
       <c r="S19" t="n">
-        <v>1.219460460382485</v>
+        <v>1.165987609497133</v>
       </c>
       <c r="T19" t="n">
-        <v>3.314841832809641</v>
+        <v>2.992257319829484</v>
       </c>
       <c r="U19" t="n">
-        <v>3.993755365678986</v>
+        <v>3.923507755219024</v>
       </c>
     </row>
     <row r="20">
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1974,28 +1974,28 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O20" t="n">
         <v>2000</v>
       </c>
       <c r="P20" t="n">
-        <v>1.989782281234678</v>
+        <v>2.036008198856143</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.547686162908299</v>
+        <v>1.847317641856994</v>
       </c>
       <c r="R20" t="n">
-        <v>0.626791256681131</v>
+        <v>0.9871601729270144</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7557126301531019</v>
+        <v>1.195211186642711</v>
       </c>
       <c r="T20" t="n">
-        <v>1.503950599182737</v>
+        <v>2.752037272669114</v>
       </c>
       <c r="U20" t="n">
-        <v>3.795212140231052</v>
+        <v>4.095038426583223</v>
       </c>
     </row>
     <row r="21">
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2051,28 +2051,28 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O21" t="n">
         <v>2000</v>
       </c>
       <c r="P21" t="n">
-        <v>2.871574828339003</v>
+        <v>2.748219514830146</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.709289515436507</v>
+        <v>2.541076867145146</v>
       </c>
       <c r="R21" t="n">
-        <v>1.067499909976965</v>
+        <v>0.9674242046966972</v>
       </c>
       <c r="S21" t="n">
-        <v>1.305177561264718</v>
+        <v>1.157099141505985</v>
       </c>
       <c r="T21" t="n">
-        <v>3.576202108553105</v>
+        <v>2.597132254059154</v>
       </c>
       <c r="U21" t="n">
-        <v>3.906196808760957</v>
+        <v>3.898854101216265</v>
       </c>
     </row>
     <row r="22">
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2128,28 +2128,28 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O22" t="n">
         <v>2000</v>
       </c>
       <c r="P22" t="n">
-        <v>2.77363389828177</v>
+        <v>2.656056446109348</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.61569387341879</v>
+        <v>2.575328283576387</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8797921849248634</v>
+        <v>0.820523440588578</v>
       </c>
       <c r="S22" t="n">
-        <v>1.13190634271867</v>
+        <v>1.074646120729132</v>
       </c>
       <c r="T22" t="n">
-        <v>2.682426529826266</v>
+        <v>3.223562676163844</v>
       </c>
       <c r="U22" t="n">
-        <v>4.282499868852448</v>
+        <v>4.381332901094976</v>
       </c>
     </row>
     <row r="23">
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2205,28 +2205,28 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O23" t="n">
         <v>2000</v>
       </c>
       <c r="P23" t="n">
-        <v>2.206417772768776</v>
+        <v>2.46279231780727</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.861201266262372</v>
+        <v>2.374073358865758</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7553985198686857</v>
+        <v>0.9853689167009071</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9797917395746353</v>
+        <v>1.220468610977745</v>
       </c>
       <c r="T23" t="n">
-        <v>2.236859989257468</v>
+        <v>2.922135909968617</v>
       </c>
       <c r="U23" t="n">
-        <v>3.769405432545011</v>
+        <v>4.001912684039135</v>
       </c>
     </row>
     <row r="24">
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2282,28 +2282,28 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O24" t="n">
         <v>2000</v>
       </c>
       <c r="P24" t="n">
-        <v>2.154781844491586</v>
+        <v>2.385545438928943</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.605383431805436</v>
+        <v>1.86086836851237</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9766862284472497</v>
+        <v>0.917771235365166</v>
       </c>
       <c r="S24" t="n">
-        <v>1.31701565242376</v>
+        <v>1.283006965413102</v>
       </c>
       <c r="T24" t="n">
-        <v>3.566062866834052</v>
+        <v>3.620725497361164</v>
       </c>
       <c r="U24" t="n">
-        <v>4.023425845154588</v>
+        <v>3.93888303504096</v>
       </c>
     </row>
     <row r="25">
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2359,28 +2359,28 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O25" t="n">
         <v>2000</v>
       </c>
       <c r="P25" t="n">
-        <v>2.437264564094857</v>
+        <v>2.255705586305765</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.639565385940725</v>
+        <v>2.41197452074797</v>
       </c>
       <c r="R25" t="n">
-        <v>0.97233379359756</v>
+        <v>0.8338980728261179</v>
       </c>
       <c r="S25" t="n">
-        <v>1.31470137590056</v>
+        <v>1.104154788113511</v>
       </c>
       <c r="T25" t="n">
-        <v>3.446766714842802</v>
+        <v>3.366651927008682</v>
       </c>
       <c r="U25" t="n">
-        <v>4.24462624539155</v>
+        <v>4.343610793360942</v>
       </c>
     </row>
     <row r="26">
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2436,28 +2436,28 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O26" t="n">
         <v>2000</v>
       </c>
       <c r="P26" t="n">
-        <v>2.747512638036014</v>
+        <v>3.100758985360488</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.769210009276581</v>
+        <v>3.174591927412523</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8322507978308415</v>
+        <v>0.9211788740406327</v>
       </c>
       <c r="S26" t="n">
-        <v>1.138846074067033</v>
+        <v>1.302264902609379</v>
       </c>
       <c r="T26" t="n">
-        <v>3.616513983855256</v>
+        <v>4.045313852811752</v>
       </c>
       <c r="U26" t="n">
-        <v>4.178937534990989</v>
+        <v>4.1708790254187</v>
       </c>
     </row>
     <row r="27">
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2513,28 +2513,28 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O27" t="n">
         <v>2000</v>
       </c>
       <c r="P27" t="n">
-        <v>1.973251241469833</v>
+        <v>1.687393564099833</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.30928283235256</v>
+        <v>1.503614232903805</v>
       </c>
       <c r="R27" t="n">
-        <v>0.6729857828645709</v>
+        <v>0.635687699943186</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8727220566860958</v>
+        <v>0.7594112430113011</v>
       </c>
       <c r="T27" t="n">
-        <v>2.412911248524694</v>
+        <v>1.586032535977743</v>
       </c>
       <c r="U27" t="n">
-        <v>4.161292166241707</v>
+        <v>4.414248640383097</v>
       </c>
     </row>
     <row r="28">
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2590,28 +2590,28 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O28" t="n">
         <v>2000</v>
       </c>
       <c r="P28" t="n">
-        <v>2.408730710611447</v>
+        <v>2.447567066632086</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.080369599219338</v>
+        <v>2.091794906353979</v>
       </c>
       <c r="R28" t="n">
-        <v>0.6259673297546444</v>
+        <v>0.673183478114728</v>
       </c>
       <c r="S28" t="n">
-        <v>0.7629053799125322</v>
+        <v>0.8215960913183002</v>
       </c>
       <c r="T28" t="n">
-        <v>2.406108210889357</v>
+        <v>2.588224151400823</v>
       </c>
       <c r="U28" t="n">
-        <v>3.703552302521585</v>
+        <v>3.697993418688065</v>
       </c>
     </row>
     <row r="29">
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2667,28 +2667,28 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O29" t="n">
         <v>2000</v>
       </c>
       <c r="P29" t="n">
-        <v>3.049701635987002</v>
+        <v>2.853061416135401</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.836458198555001</v>
+        <v>2.438718515472454</v>
       </c>
       <c r="R29" t="n">
-        <v>0.9801773642513204</v>
+        <v>0.8687626850113869</v>
       </c>
       <c r="S29" t="n">
-        <v>1.236449139817213</v>
+        <v>1.07172821140901</v>
       </c>
       <c r="T29" t="n">
-        <v>2.747468079849398</v>
+        <v>2.512314439780525</v>
       </c>
       <c r="U29" t="n">
-        <v>4.20152259289394</v>
+        <v>4.066852554861917</v>
       </c>
     </row>
     <row r="30">
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2744,28 +2744,28 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O30" t="n">
         <v>2000</v>
       </c>
       <c r="P30" t="n">
-        <v>2.862338064958696</v>
+        <v>2.812004085024722</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.847960992921322</v>
+        <v>2.835473341715701</v>
       </c>
       <c r="R30" t="n">
-        <v>1.069965471117767</v>
+        <v>0.9698672206178848</v>
       </c>
       <c r="S30" t="n">
-        <v>1.379933865419604</v>
+        <v>1.232224697605437</v>
       </c>
       <c r="T30" t="n">
-        <v>3.689499401443641</v>
+        <v>3.31272496629451</v>
       </c>
       <c r="U30" t="n">
-        <v>4.121852634289924</v>
+        <v>4.090946197100806</v>
       </c>
     </row>
     <row r="31">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2821,28 +2821,28 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O31" t="n">
         <v>2000</v>
       </c>
       <c r="P31" t="n">
-        <v>2.544476479368264</v>
+        <v>2.211492819017874</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.546447472988119</v>
+        <v>2.171183170974555</v>
       </c>
       <c r="R31" t="n">
-        <v>0.9626148846006718</v>
+        <v>0.9256319969908136</v>
       </c>
       <c r="S31" t="n">
-        <v>1.424634132000993</v>
+        <v>1.295311330543687</v>
       </c>
       <c r="T31" t="n">
-        <v>4.524833128599298</v>
+        <v>3.726432239958889</v>
       </c>
       <c r="U31" t="n">
-        <v>3.984187776092178</v>
+        <v>3.727504414040973</v>
       </c>
     </row>
     <row r="32">
@@ -2866,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2898,28 +2898,28 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O32" t="n">
         <v>2000</v>
       </c>
       <c r="P32" t="n">
-        <v>3.246358721742365</v>
+        <v>3.497231095288744</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.012530195887164</v>
+        <v>3.488661096933753</v>
       </c>
       <c r="R32" t="n">
-        <v>1.034771741219683</v>
+        <v>1.02774758521878</v>
       </c>
       <c r="S32" t="n">
-        <v>1.338749344908672</v>
+        <v>1.290734265964935</v>
       </c>
       <c r="T32" t="n">
-        <v>4.079404496138658</v>
+        <v>3.672674125369312</v>
       </c>
       <c r="U32" t="n">
-        <v>4.210014821523496</v>
+        <v>4.296828840835227</v>
       </c>
     </row>
     <row r="33">
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2975,28 +2975,28 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O33" t="n">
         <v>2000</v>
       </c>
       <c r="P33" t="n">
-        <v>3.360342672497357</v>
+        <v>2.933628640525362</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.457906670532118</v>
+        <v>2.877778214927688</v>
       </c>
       <c r="R33" t="n">
-        <v>1.08401737525222</v>
+        <v>0.9898531044025544</v>
       </c>
       <c r="S33" t="n">
-        <v>1.410303783179736</v>
+        <v>1.27998250370209</v>
       </c>
       <c r="T33" t="n">
-        <v>3.469986215884504</v>
+        <v>3.2017516480756</v>
       </c>
       <c r="U33" t="n">
-        <v>3.908656906743546</v>
+        <v>4.099343704815616</v>
       </c>
     </row>
     <row r="34">
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3052,28 +3052,28 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O34" t="n">
         <v>2000</v>
       </c>
       <c r="P34" t="n">
-        <v>2.310899702875481</v>
+        <v>2.456823362329149</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.856058216286885</v>
+        <v>2.260793297082203</v>
       </c>
       <c r="R34" t="n">
-        <v>0.9049635124295744</v>
+        <v>0.8792888727768859</v>
       </c>
       <c r="S34" t="n">
-        <v>1.269368314406909</v>
+        <v>1.269642329009794</v>
       </c>
       <c r="T34" t="n">
-        <v>2.92113939923221</v>
+        <v>3.384338089573028</v>
       </c>
       <c r="U34" t="n">
-        <v>4.081304706616837</v>
+        <v>4.039090384066133</v>
       </c>
     </row>
     <row r="35">
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3129,28 +3129,28 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O35" t="n">
         <v>2000</v>
       </c>
       <c r="P35" t="n">
-        <v>2.043908360675574</v>
+        <v>2.256126068517693</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.963571720990914</v>
+        <v>1.838628073241604</v>
       </c>
       <c r="R35" t="n">
-        <v>0.5169391969994374</v>
+        <v>0.5249936145999845</v>
       </c>
       <c r="S35" t="n">
-        <v>0.5793151532975079</v>
+        <v>0.6245631032859191</v>
       </c>
       <c r="T35" t="n">
-        <v>1.376001496787381</v>
+        <v>1.667555018060064</v>
       </c>
       <c r="U35" t="n">
-        <v>3.537230772188373</v>
+        <v>3.388035985557829</v>
       </c>
     </row>
     <row r="36">
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3206,28 +3206,28 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O36" t="n">
         <v>2000</v>
       </c>
       <c r="P36" t="n">
-        <v>2.410181286731864</v>
+        <v>2.167307014494638</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.861511910530114</v>
+        <v>1.470293821792144</v>
       </c>
       <c r="R36" t="n">
-        <v>1.133561288999753</v>
+        <v>0.9637409849507549</v>
       </c>
       <c r="S36" t="n">
-        <v>1.405360242031357</v>
+        <v>1.263903195195651</v>
       </c>
       <c r="T36" t="n">
-        <v>3.068515840241531</v>
+        <v>3.218676061840348</v>
       </c>
       <c r="U36" t="n">
-        <v>4.292574340387337</v>
+        <v>4.21883818263249</v>
       </c>
     </row>
     <row r="37">
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3283,28 +3283,28 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O37" t="n">
         <v>2000</v>
       </c>
       <c r="P37" t="n">
-        <v>3.060815924657026</v>
+        <v>2.926928535355509</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.816757022374975</v>
+        <v>2.566907189926699</v>
       </c>
       <c r="R37" t="n">
-        <v>1.317438119565198</v>
+        <v>1.133198525705437</v>
       </c>
       <c r="S37" t="n">
-        <v>1.675528300655896</v>
+        <v>1.48849033898188</v>
       </c>
       <c r="T37" t="n">
-        <v>4.222476489561551</v>
+        <v>3.728409532069733</v>
       </c>
       <c r="U37" t="n">
-        <v>4.50198386071758</v>
+        <v>4.248694374509213</v>
       </c>
     </row>
     <row r="38">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3360,28 +3360,28 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O38" t="n">
         <v>2000</v>
       </c>
       <c r="P38" t="n">
-        <v>2.591599622801243</v>
+        <v>2.465859880850371</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.421969107084283</v>
+        <v>2.440321067514025</v>
       </c>
       <c r="R38" t="n">
-        <v>0.9749673975973449</v>
+        <v>0.8727006235618265</v>
       </c>
       <c r="S38" t="n">
-        <v>1.159459862175515</v>
+        <v>1.083898855468333</v>
       </c>
       <c r="T38" t="n">
-        <v>2.943786362406584</v>
+        <v>2.740958947929066</v>
       </c>
       <c r="U38" t="n">
-        <v>3.706357729499428</v>
+        <v>3.799867027313473</v>
       </c>
     </row>
     <row r="39">
@@ -3405,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3437,28 +3437,28 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O39" t="n">
         <v>2000</v>
       </c>
       <c r="P39" t="n">
-        <v>2.449472658400951</v>
+        <v>2.720007373354473</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.888759601847378</v>
+        <v>2.07811864144816</v>
       </c>
       <c r="R39" t="n">
-        <v>0.9137879796081214</v>
+        <v>1.182776730119356</v>
       </c>
       <c r="S39" t="n">
-        <v>1.203412930119001</v>
+        <v>1.638716614057058</v>
       </c>
       <c r="T39" t="n">
-        <v>3.679703577663687</v>
+        <v>3.999157073700168</v>
       </c>
       <c r="U39" t="n">
-        <v>4.183368233359644</v>
+        <v>4.500014616348543</v>
       </c>
     </row>
     <row r="40">
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3514,28 +3514,28 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O40" t="n">
         <v>2000</v>
       </c>
       <c r="P40" t="n">
-        <v>2.484634306903329</v>
+        <v>2.809334454979908</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.46894076839617</v>
+        <v>2.469312014583904</v>
       </c>
       <c r="R40" t="n">
-        <v>1.094343972995902</v>
+        <v>1.126023751124678</v>
       </c>
       <c r="S40" t="n">
-        <v>1.686641811811114</v>
+        <v>1.673814950342652</v>
       </c>
       <c r="T40" t="n">
-        <v>4.415492697203128</v>
+        <v>4.510137931514549</v>
       </c>
       <c r="U40" t="n">
-        <v>3.819917662419754</v>
+        <v>3.695103283341409</v>
       </c>
     </row>
     <row r="41">
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3591,28 +3591,28 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O41" t="n">
         <v>2000</v>
       </c>
       <c r="P41" t="n">
-        <v>2.088481980569139</v>
+        <v>2.245324917656357</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.152807923994344</v>
+        <v>2.480563326388625</v>
       </c>
       <c r="R41" t="n">
-        <v>0.6383415266807814</v>
+        <v>0.6901123187343777</v>
       </c>
       <c r="S41" t="n">
-        <v>0.8305703560324035</v>
+        <v>0.8826865091211498</v>
       </c>
       <c r="T41" t="n">
-        <v>1.965321831722754</v>
+        <v>2.086468948543065</v>
       </c>
       <c r="U41" t="n">
-        <v>4.041033123297999</v>
+        <v>4.132346223390015</v>
       </c>
     </row>
     <row r="42">
@@ -3636,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3668,28 +3668,28 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O42" t="n">
         <v>2000</v>
       </c>
       <c r="P42" t="n">
-        <v>2.272992462231506</v>
+        <v>2.36023475739134</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.343601083051832</v>
+        <v>2.342740954443879</v>
       </c>
       <c r="R42" t="n">
-        <v>0.8797087365018674</v>
+        <v>0.8026936037807402</v>
       </c>
       <c r="S42" t="n">
-        <v>1.196453675056532</v>
+        <v>1.054591686771655</v>
       </c>
       <c r="T42" t="n">
-        <v>2.86368290049392</v>
+        <v>2.481236935593024</v>
       </c>
       <c r="U42" t="n">
-        <v>4.500460530533847</v>
+        <v>4.602707819728785</v>
       </c>
     </row>
     <row r="43">
@@ -3713,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3745,28 +3745,28 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O43" t="n">
         <v>2000</v>
       </c>
       <c r="P43" t="n">
-        <v>1.930979729412205</v>
+        <v>2.281559525086785</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.770641998416644</v>
+        <v>1.659473051766471</v>
       </c>
       <c r="R43" t="n">
-        <v>0.9852370597772362</v>
+        <v>1.018558098733797</v>
       </c>
       <c r="S43" t="n">
-        <v>1.401889075436591</v>
+        <v>1.435043542842443</v>
       </c>
       <c r="T43" t="n">
-        <v>4.019104237876398</v>
+        <v>4.044629767979643</v>
       </c>
       <c r="U43" t="n">
-        <v>3.70644667751334</v>
+        <v>3.598376514145901</v>
       </c>
     </row>
     <row r="44">
@@ -3790,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3822,28 +3822,28 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O44" t="n">
         <v>2000</v>
       </c>
       <c r="P44" t="n">
-        <v>2.632542523830796</v>
+        <v>2.859456891759006</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.07810241405569</v>
+        <v>2.777146917002052</v>
       </c>
       <c r="R44" t="n">
-        <v>0.9561423806101036</v>
+        <v>1.067472174712771</v>
       </c>
       <c r="S44" t="n">
-        <v>1.084947395310683</v>
+        <v>1.312342331124505</v>
       </c>
       <c r="T44" t="n">
-        <v>2.376285519762654</v>
+        <v>3.737281675684677</v>
       </c>
       <c r="U44" t="n">
-        <v>3.950848554732076</v>
+        <v>4.303577310768185</v>
       </c>
     </row>
     <row r="45">
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3899,28 +3899,28 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O45" t="n">
         <v>2000</v>
       </c>
       <c r="P45" t="n">
-        <v>2.876204929860643</v>
+        <v>3.030078697208451</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.624628008287261</v>
+        <v>2.571945040086828</v>
       </c>
       <c r="R45" t="n">
-        <v>0.9628334801134454</v>
+        <v>0.9424423273140728</v>
       </c>
       <c r="S45" t="n">
-        <v>1.205858272676143</v>
+        <v>1.154328473117038</v>
       </c>
       <c r="T45" t="n">
-        <v>3.486905332101109</v>
+        <v>2.900546571504705</v>
       </c>
       <c r="U45" t="n">
-        <v>3.966631893953096</v>
+        <v>3.820641856300295</v>
       </c>
     </row>
     <row r="46">
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3976,28 +3976,28 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O46" t="n">
         <v>2000</v>
       </c>
       <c r="P46" t="n">
-        <v>2.48656978696414</v>
+        <v>2.069979718718242</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.862675637419892</v>
+        <v>1.621620695512991</v>
       </c>
       <c r="R46" t="n">
-        <v>0.6558450280608183</v>
+        <v>0.591100942046058</v>
       </c>
       <c r="S46" t="n">
-        <v>0.9895903001185483</v>
+        <v>0.9416407514282646</v>
       </c>
       <c r="T46" t="n">
-        <v>2.50587097204702</v>
+        <v>2.66671560277311</v>
       </c>
       <c r="U46" t="n">
-        <v>3.482325436398054</v>
+        <v>3.186245024787728</v>
       </c>
     </row>
     <row r="47">
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -4053,28 +4053,28 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O47" t="n">
         <v>2000</v>
       </c>
       <c r="P47" t="n">
-        <v>2.937549040994939</v>
+        <v>2.593295860051856</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.316188323071422</v>
+        <v>2.404866774755832</v>
       </c>
       <c r="R47" t="n">
-        <v>1.024530933798933</v>
+        <v>0.8562512317113257</v>
       </c>
       <c r="S47" t="n">
-        <v>1.34907972449983</v>
+        <v>1.058606767017767</v>
       </c>
       <c r="T47" t="n">
-        <v>4.098768494069155</v>
+        <v>2.381344079957266</v>
       </c>
       <c r="U47" t="n">
-        <v>3.979812247211163</v>
+        <v>4.045552738093291</v>
       </c>
     </row>
     <row r="48">
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4130,28 +4130,28 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O48" t="n">
         <v>2000</v>
       </c>
       <c r="P48" t="n">
-        <v>2.542711791667637</v>
+        <v>3.216313007938071</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.303305905415259</v>
+        <v>2.903706544253938</v>
       </c>
       <c r="R48" t="n">
-        <v>1.041732657761286</v>
+        <v>1.47989445569794</v>
       </c>
       <c r="S48" t="n">
-        <v>1.366900938702316</v>
+        <v>1.879261113809578</v>
       </c>
       <c r="T48" t="n">
-        <v>3.021058281249559</v>
+        <v>4.567287543854938</v>
       </c>
       <c r="U48" t="n">
-        <v>4.060125462427894</v>
+        <v>4.343302152552829</v>
       </c>
     </row>
     <row r="49">
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4207,28 +4207,28 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O49" t="n">
         <v>2000</v>
       </c>
       <c r="P49" t="n">
-        <v>2.872784856632773</v>
+        <v>2.818976054104306</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.484481359533715</v>
+        <v>2.412212322446318</v>
       </c>
       <c r="R49" t="n">
-        <v>0.7936141435024562</v>
+        <v>0.8063572964993344</v>
       </c>
       <c r="S49" t="n">
-        <v>1.138397403024661</v>
+        <v>1.17095766176408</v>
       </c>
       <c r="T49" t="n">
-        <v>3.411397876930288</v>
+        <v>3.50238639062075</v>
       </c>
       <c r="U49" t="n">
-        <v>3.748112355495783</v>
+        <v>3.803451984037251</v>
       </c>
     </row>
     <row r="50">
@@ -4252,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4284,28 +4284,28 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O50" t="n">
         <v>2000</v>
       </c>
       <c r="P50" t="n">
-        <v>2.085049755485441</v>
+        <v>2.221386143660891</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.950904893334346</v>
+        <v>1.988675445686137</v>
       </c>
       <c r="R50" t="n">
-        <v>0.7961089646178234</v>
+        <v>0.7317117097185312</v>
       </c>
       <c r="S50" t="n">
-        <v>1.123807981391233</v>
+        <v>1.008165855575936</v>
       </c>
       <c r="T50" t="n">
-        <v>3.088316895263546</v>
+        <v>2.499039700848073</v>
       </c>
       <c r="U50" t="n">
-        <v>4.035362416326175</v>
+        <v>3.661167245750547</v>
       </c>
     </row>
     <row r="51">
@@ -4329,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4361,28 +4361,28 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="O51" t="n">
         <v>2000</v>
       </c>
       <c r="P51" t="n">
-        <v>2.75547505231888</v>
+        <v>2.556885548081274</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.580285672224648</v>
+        <v>2.303885733593058</v>
       </c>
       <c r="R51" t="n">
-        <v>0.7733053494794406</v>
+        <v>0.8734821525928995</v>
       </c>
       <c r="S51" t="n">
-        <v>0.9189715080327322</v>
+        <v>1.052138605728802</v>
       </c>
       <c r="T51" t="n">
-        <v>2.193644707384593</v>
+        <v>2.765771641362882</v>
       </c>
       <c r="U51" t="n">
-        <v>3.809297378005201</v>
+        <v>3.756462284107928</v>
       </c>
     </row>
   </sheetData>
